--- a/data/synthetic_marketplace_projection_model.xlsx
+++ b/data/synthetic_marketplace_projection_model.xlsx
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F15">
         <f>$B$8</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G15">
         <f>ROUND(IF(ROW()=15,0,J14)*F15,0)</f>
@@ -11680,11 +11680,11 @@
       </c>
       <c r="F16">
         <f>F15+($B$9-F15)*$B$10</f>
-        <v>0.218</v>
+        <v>0.318</v>
       </c>
       <c r="G16">
         <f>ROUND(IF(ROW()=15,0,J15)*F16,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <f>ROUND(MAX(0,J16-G16),0)</f>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="I16">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J15)-G16),0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <f>ROUND(MAX(G16,D16*E16),0)</f>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17">
         <f>F16+($B$9-F16)*$B$10</f>
-        <v>0.2349</v>
+        <v>0.3349</v>
       </c>
       <c r="G17">
         <f>ROUND(IF(ROW()=15,0,J16)*F17,0)</f>
@@ -11739,11 +11739,11 @@
       </c>
       <c r="H17">
         <f>ROUND(MAX(0,J17-G17),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J16)-G17),0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <f>ROUND(MAX(G17,D17*E17),0)</f>
@@ -11782,19 +11782,19 @@
       </c>
       <c r="F18">
         <f>F17+($B$9-F17)*$B$10</f>
-        <v>0.2508</v>
+        <v>0.3508</v>
       </c>
       <c r="G18">
         <f>ROUND(IF(ROW()=15,0,J17)*F18,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <f>ROUND(MAX(0,J18-G18),0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J17)-G18),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <f>ROUND(MAX(G18,D18*E18),0)</f>
@@ -11833,19 +11833,19 @@
       </c>
       <c r="F19">
         <f>F18+($B$9-F18)*$B$10</f>
-        <v>0.2658</v>
+        <v>0.3658</v>
       </c>
       <c r="G19">
         <f>ROUND(IF(ROW()=15,0,J18)*F19,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <f>ROUND(MAX(0,J19-G19),0)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I19">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J18)-G19),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <f>ROUND(MAX(G19,D19*E19),0)</f>
@@ -11884,19 +11884,19 @@
       </c>
       <c r="F20">
         <f>F19+($B$9-F19)*$B$10</f>
-        <v>0.2798</v>
+        <v>0.3798</v>
       </c>
       <c r="G20">
         <f>ROUND(IF(ROW()=15,0,J19)*F20,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <f>ROUND(MAX(0,J20-G20),0)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I20">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J19)-G20),0)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <f>ROUND(MAX(G20,D20*E20),0)</f>
@@ -11935,19 +11935,19 @@
       </c>
       <c r="F21">
         <f>F20+($B$9-F20)*$B$10</f>
-        <v>0.293</v>
+        <v>0.393</v>
       </c>
       <c r="G21">
         <f>ROUND(IF(ROW()=15,0,J20)*F21,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <f>ROUND(MAX(0,J21-G21),0)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I21">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J20)-G21),0)</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J21">
         <f>ROUND(MAX(G21,D21*E21),0)</f>
@@ -11986,19 +11986,19 @@
       </c>
       <c r="F22">
         <f>F21+($B$9-F21)*$B$10</f>
-        <v>0.3055</v>
+        <v>0.4055</v>
       </c>
       <c r="G22">
         <f>ROUND(IF(ROW()=15,0,J21)*F22,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <f>ROUND(MAX(0,J22-G22),0)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I22">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J21)-G22),0)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J22">
         <f>ROUND(MAX(G22,D22*E22),0)</f>
@@ -12037,19 +12037,19 @@
       </c>
       <c r="F23">
         <f>F22+($B$9-F22)*$B$10</f>
-        <v>0.3171</v>
+        <v>0.4171</v>
       </c>
       <c r="G23">
         <f>ROUND(IF(ROW()=15,0,J22)*F23,0)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H23">
         <f>ROUND(MAX(0,J23-G23),0)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I23">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J22)-G23),0)</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J23">
         <f>ROUND(MAX(G23,D23*E23),0)</f>
@@ -12088,19 +12088,19 @@
       </c>
       <c r="F24">
         <f>F23+($B$9-F23)*$B$10</f>
-        <v>0.3281</v>
+        <v>0.4281</v>
       </c>
       <c r="G24">
         <f>ROUND(IF(ROW()=15,0,J23)*F24,0)</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H24">
         <f>ROUND(MAX(0,J24-G24),0)</f>
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I24">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J23)-G24),0)</f>
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J24">
         <f>ROUND(MAX(G24,D24*E24),0)</f>
@@ -12139,19 +12139,19 @@
       </c>
       <c r="F25">
         <f>F24+($B$9-F24)*$B$10</f>
-        <v>0.3384</v>
+        <v>0.4384</v>
       </c>
       <c r="G25">
         <f>ROUND(IF(ROW()=15,0,J24)*F25,0)</f>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H25">
         <f>ROUND(MAX(0,J25-G25),0)</f>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I25">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J24)-G25),0)</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J25">
         <f>ROUND(MAX(G25,D25*E25),0)</f>
@@ -12190,19 +12190,19 @@
       </c>
       <c r="F26">
         <f>F25+($B$9-F25)*$B$10</f>
-        <v>0.3481</v>
+        <v>0.4481</v>
       </c>
       <c r="G26">
         <f>ROUND(IF(ROW()=15,0,J25)*F26,0)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H26">
         <f>ROUND(MAX(0,J26-G26),0)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I26">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J25)-G26),0)</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J26">
         <f>ROUND(MAX(G26,D26*E26),0)</f>
@@ -12241,19 +12241,19 @@
       </c>
       <c r="F27">
         <f>F26+($B$9-F26)*$B$10</f>
-        <v>0.3572</v>
+        <v>0.4572</v>
       </c>
       <c r="G27">
         <f>ROUND(IF(ROW()=15,0,J26)*F27,0)</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H27">
         <f>ROUND(MAX(0,J27-G27),0)</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I27">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J26)-G27),0)</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J27">
         <f>ROUND(MAX(G27,D27*E27),0)</f>
@@ -12292,19 +12292,19 @@
       </c>
       <c r="F28">
         <f>F27+($B$9-F27)*$B$10</f>
-        <v>0.3658</v>
+        <v>0.4658</v>
       </c>
       <c r="G28">
         <f>ROUND(IF(ROW()=15,0,J27)*F28,0)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H28">
         <f>ROUND(MAX(0,J28-G28),0)</f>
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I28">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J27)-G28),0)</f>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J28">
         <f>ROUND(MAX(G28,D28*E28),0)</f>
@@ -12343,19 +12343,19 @@
       </c>
       <c r="F29">
         <f>F28+($B$9-F28)*$B$10</f>
-        <v>0.3738</v>
+        <v>0.4738</v>
       </c>
       <c r="G29">
         <f>ROUND(IF(ROW()=15,0,J28)*F29,0)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H29">
         <f>ROUND(MAX(0,J29-G29),0)</f>
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I29">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J28)-G29),0)</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J29">
         <f>ROUND(MAX(G29,D29*E29),0)</f>
@@ -12394,19 +12394,19 @@
       </c>
       <c r="F30">
         <f>F29+($B$9-F29)*$B$10</f>
-        <v>0.3814</v>
+        <v>0.4814</v>
       </c>
       <c r="G30">
         <f>ROUND(IF(ROW()=15,0,J29)*F30,0)</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H30">
         <f>ROUND(MAX(0,J30-G30),0)</f>
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I30">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J29)-G30),0)</f>
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J30">
         <f>ROUND(MAX(G30,D30*E30),0)</f>
@@ -12445,19 +12445,19 @@
       </c>
       <c r="F31">
         <f>F30+($B$9-F30)*$B$10</f>
-        <v>0.3885</v>
+        <v>0.4885</v>
       </c>
       <c r="G31">
         <f>ROUND(IF(ROW()=15,0,J30)*F31,0)</f>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H31">
         <f>ROUND(MAX(0,J31-G31),0)</f>
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I31">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J30)-G31),0)</f>
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J31">
         <f>ROUND(MAX(G31,D31*E31),0)</f>
@@ -12496,19 +12496,19 @@
       </c>
       <c r="F32">
         <f>F31+($B$9-F31)*$B$10</f>
-        <v>0.3952</v>
+        <v>0.4952</v>
       </c>
       <c r="G32">
         <f>ROUND(IF(ROW()=15,0,J31)*F32,0)</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H32">
         <f>ROUND(MAX(0,J32-G32),0)</f>
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I32">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J31)-G32),0)</f>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J32">
         <f>ROUND(MAX(G32,D32*E32),0)</f>
@@ -12547,19 +12547,19 @@
       </c>
       <c r="F33">
         <f>F32+($B$9-F32)*$B$10</f>
-        <v>0.4015</v>
+        <v>0.5015</v>
       </c>
       <c r="G33">
         <f>ROUND(IF(ROW()=15,0,J32)*F33,0)</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H33">
         <f>ROUND(MAX(0,J33-G33),0)</f>
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I33">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J32)-G33),0)</f>
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J33">
         <f>ROUND(MAX(G33,D33*E33),0)</f>
@@ -12598,19 +12598,19 @@
       </c>
       <c r="F34">
         <f>F33+($B$9-F33)*$B$10</f>
-        <v>0.4074</v>
+        <v>0.5074</v>
       </c>
       <c r="G34">
         <f>ROUND(IF(ROW()=15,0,J33)*F34,0)</f>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H34">
         <f>ROUND(MAX(0,J34-G34),0)</f>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I34">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J33)-G34),0)</f>
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J34">
         <f>ROUND(MAX(G34,D34*E34),0)</f>
@@ -12649,19 +12649,19 @@
       </c>
       <c r="F35">
         <f>F34+($B$9-F34)*$B$10</f>
-        <v>0.413</v>
+        <v>0.513</v>
       </c>
       <c r="G35">
         <f>ROUND(IF(ROW()=15,0,J34)*F35,0)</f>
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H35">
         <f>ROUND(MAX(0,J35-G35),0)</f>
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I35">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J34)-G35),0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J35">
         <f>ROUND(MAX(G35,D35*E35),0)</f>
@@ -12700,19 +12700,19 @@
       </c>
       <c r="F36">
         <f>F35+($B$9-F35)*$B$10</f>
-        <v>0.4182</v>
+        <v>0.5182</v>
       </c>
       <c r="G36">
         <f>ROUND(IF(ROW()=15,0,J35)*F36,0)</f>
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H36">
         <f>ROUND(MAX(0,J36-G36),0)</f>
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I36">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J35)-G36),0)</f>
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J36">
         <f>ROUND(MAX(G36,D36*E36),0)</f>
@@ -12751,19 +12751,19 @@
       </c>
       <c r="F37">
         <f>F36+($B$9-F36)*$B$10</f>
-        <v>0.4231</v>
+        <v>0.5231</v>
       </c>
       <c r="G37">
         <f>ROUND(IF(ROW()=15,0,J36)*F37,0)</f>
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="H37">
         <f>ROUND(MAX(0,J37-G37),0)</f>
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I37">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J36)-G37),0)</f>
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="J37">
         <f>ROUND(MAX(G37,D37*E37),0)</f>
@@ -12802,19 +12802,19 @@
       </c>
       <c r="F38">
         <f>F37+($B$9-F37)*$B$10</f>
-        <v>0.4277</v>
+        <v>0.5277</v>
       </c>
       <c r="G38">
         <f>ROUND(IF(ROW()=15,0,J37)*F38,0)</f>
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H38">
         <f>ROUND(MAX(0,J38-G38),0)</f>
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="I38">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J37)-G38),0)</f>
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="J38">
         <f>ROUND(MAX(G38,D38*E38),0)</f>
@@ -12853,19 +12853,19 @@
       </c>
       <c r="F39">
         <f>F38+($B$9-F38)*$B$10</f>
-        <v>0.432</v>
+        <v>0.532</v>
       </c>
       <c r="G39">
         <f>ROUND(IF(ROW()=15,0,J38)*F39,0)</f>
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H39">
         <f>ROUND(MAX(0,J39-G39),0)</f>
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I39">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J38)-G39),0)</f>
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="J39">
         <f>ROUND(MAX(G39,D39*E39),0)</f>
@@ -12904,19 +12904,19 @@
       </c>
       <c r="F40">
         <f>F39+($B$9-F39)*$B$10</f>
-        <v>0.4361</v>
+        <v>0.5361</v>
       </c>
       <c r="G40">
         <f>ROUND(IF(ROW()=15,0,J39)*F40,0)</f>
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="H40">
         <f>ROUND(MAX(0,J40-G40),0)</f>
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I40">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J39)-G40),0)</f>
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="J40">
         <f>ROUND(MAX(G40,D40*E40),0)</f>
@@ -12955,19 +12955,19 @@
       </c>
       <c r="F41">
         <f>F40+($B$9-F40)*$B$10</f>
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="G41">
         <f>ROUND(IF(ROW()=15,0,J40)*F41,0)</f>
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H41">
         <f>ROUND(MAX(0,J41-G41),0)</f>
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I41">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J40)-G41),0)</f>
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J41">
         <f>ROUND(MAX(G41,D41*E41),0)</f>
@@ -13006,19 +13006,19 @@
       </c>
       <c r="F42">
         <f>F41+($B$9-F41)*$B$10</f>
-        <v>0.4436</v>
+        <v>0.5436</v>
       </c>
       <c r="G42">
         <f>ROUND(IF(ROW()=15,0,J41)*F42,0)</f>
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H42">
         <f>ROUND(MAX(0,J42-G42),0)</f>
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I42">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J41)-G42),0)</f>
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="J42">
         <f>ROUND(MAX(G42,D42*E42),0)</f>
@@ -13057,19 +13057,19 @@
       </c>
       <c r="F43">
         <f>F42+($B$9-F42)*$B$10</f>
-        <v>0.4469</v>
+        <v>0.5469</v>
       </c>
       <c r="G43">
         <f>ROUND(IF(ROW()=15,0,J42)*F43,0)</f>
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H43">
         <f>ROUND(MAX(0,J43-G43),0)</f>
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="I43">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J42)-G43),0)</f>
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J43">
         <f>ROUND(MAX(G43,D43*E43),0)</f>
@@ -13108,19 +13108,19 @@
       </c>
       <c r="F44">
         <f>F43+($B$9-F43)*$B$10</f>
-        <v>0.4501</v>
+        <v>0.5501</v>
       </c>
       <c r="G44">
         <f>ROUND(IF(ROW()=15,0,J43)*F44,0)</f>
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H44">
         <f>ROUND(MAX(0,J44-G44),0)</f>
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I44">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J43)-G44),0)</f>
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J44">
         <f>ROUND(MAX(G44,D44*E44),0)</f>
@@ -13159,19 +13159,19 @@
       </c>
       <c r="F45">
         <f>F44+($B$9-F44)*$B$10</f>
-        <v>0.4531</v>
+        <v>0.5531</v>
       </c>
       <c r="G45">
         <f>ROUND(IF(ROW()=15,0,J44)*F45,0)</f>
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="H45">
         <f>ROUND(MAX(0,J45-G45),0)</f>
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I45">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J44)-G45),0)</f>
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="J45">
         <f>ROUND(MAX(G45,D45*E45),0)</f>
@@ -13210,19 +13210,19 @@
       </c>
       <c r="F46">
         <f>F45+($B$9-F45)*$B$10</f>
-        <v>0.4559</v>
+        <v>0.5559</v>
       </c>
       <c r="G46">
         <f>ROUND(IF(ROW()=15,0,J45)*F46,0)</f>
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="H46">
         <f>ROUND(MAX(0,J46-G46),0)</f>
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="I46">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J45)-G46),0)</f>
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="J46">
         <f>ROUND(MAX(G46,D46*E46),0)</f>
@@ -13261,19 +13261,19 @@
       </c>
       <c r="F47">
         <f>F46+($B$9-F46)*$B$10</f>
-        <v>0.4586</v>
+        <v>0.5586</v>
       </c>
       <c r="G47">
         <f>ROUND(IF(ROW()=15,0,J46)*F47,0)</f>
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="H47">
         <f>ROUND(MAX(0,J47-G47),0)</f>
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="I47">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J46)-G47),0)</f>
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="J47">
         <f>ROUND(MAX(G47,D47*E47),0)</f>
@@ -13312,19 +13312,19 @@
       </c>
       <c r="F48">
         <f>F47+($B$9-F47)*$B$10</f>
-        <v>0.4611</v>
+        <v>0.5611</v>
       </c>
       <c r="G48">
         <f>ROUND(IF(ROW()=15,0,J47)*F48,0)</f>
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="H48">
         <f>ROUND(MAX(0,J48-G48),0)</f>
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="I48">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J47)-G48),0)</f>
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="J48">
         <f>ROUND(MAX(G48,D48*E48),0)</f>
@@ -13363,19 +13363,19 @@
       </c>
       <c r="F49">
         <f>F48+($B$9-F48)*$B$10</f>
-        <v>0.4634</v>
+        <v>0.5634</v>
       </c>
       <c r="G49">
         <f>ROUND(IF(ROW()=15,0,J48)*F49,0)</f>
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="H49">
         <f>ROUND(MAX(0,J49-G49),0)</f>
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I49">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J48)-G49),0)</f>
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="J49">
         <f>ROUND(MAX(G49,D49*E49),0)</f>
@@ -13414,19 +13414,19 @@
       </c>
       <c r="F50">
         <f>F49+($B$9-F49)*$B$10</f>
-        <v>0.4656</v>
+        <v>0.5656</v>
       </c>
       <c r="G50">
         <f>ROUND(IF(ROW()=15,0,J49)*F50,0)</f>
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="H50">
         <f>ROUND(MAX(0,J50-G50),0)</f>
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="I50">
         <f>ROUND(MAX(0,IF(ROW()=15,0,J49)-G50),0)</f>
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="J50">
         <f>ROUND(MAX(G50,D50*E50),0)</f>
